--- a/GRID_TO_LOAD.xlsx
+++ b/GRID_TO_LOAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhino\Documents\PROJEKTS JS\Mapping is boring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA680259-53F8-47E2-B0D4-39C8566150F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D97596-A314-41D5-9E2E-7968955A1168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="18" activeTab="20" xr2:uid="{B34349A9-D588-42E5-9EA3-3BAC4BC5A281}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="13" xr2:uid="{B34349A9-D588-42E5-9EA3-3BAC4BC5A281}"/>
   </bookViews>
   <sheets>
     <sheet name="VN Alfa Romeo" sheetId="13" r:id="rId1"/>
@@ -22789,10 +22789,10 @@
         <v>12977</v>
       </c>
       <c r="G6" s="17">
-        <v>12978</v>
+        <v>-12978</v>
       </c>
       <c r="H6" s="17">
-        <v>12979</v>
+        <v>-12979</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22815,10 +22815,10 @@
         <v>12983</v>
       </c>
       <c r="G7" s="17">
-        <v>12984</v>
+        <v>-12984</v>
       </c>
       <c r="H7" s="17">
-        <v>12985</v>
+        <v>-12985</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22829,22 +22829,22 @@
         <v>1973</v>
       </c>
       <c r="C8" s="17">
-        <v>12986</v>
+        <v>-12986</v>
       </c>
       <c r="D8" s="17">
-        <v>12987</v>
+        <v>-12987</v>
       </c>
       <c r="E8" s="17">
-        <v>12988</v>
+        <v>-12988</v>
       </c>
       <c r="F8" s="17">
-        <v>12989</v>
+        <v>-12989</v>
       </c>
       <c r="G8" s="17">
-        <v>12990</v>
+        <v>-12990</v>
       </c>
       <c r="H8" s="17">
-        <v>12991</v>
+        <v>-12991</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -22867,10 +22867,10 @@
         <v>12995</v>
       </c>
       <c r="G9" s="17">
-        <v>12996</v>
+        <v>-12996</v>
       </c>
       <c r="H9" s="17">
-        <v>12997</v>
+        <v>-12997</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22893,10 +22893,10 @@
         <v>13007</v>
       </c>
       <c r="G10" s="17">
-        <v>13008</v>
+        <v>-13008</v>
       </c>
       <c r="H10" s="17">
-        <v>13009</v>
+        <v>-13009</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -22919,10 +22919,10 @@
         <v>13013</v>
       </c>
       <c r="G11" s="17">
-        <v>13014</v>
+        <v>-13014</v>
       </c>
       <c r="H11" s="17">
-        <v>13015</v>
+        <v>-13015</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22945,10 +22945,10 @@
         <v>13019</v>
       </c>
       <c r="G12" s="17">
-        <v>13020</v>
+        <v>-13020</v>
       </c>
       <c r="H12" s="17">
-        <v>13021</v>
+        <v>-13021</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22959,22 +22959,22 @@
         <v>1963</v>
       </c>
       <c r="C13" s="17">
-        <v>13022</v>
+        <v>-13022</v>
       </c>
       <c r="D13" s="17">
-        <v>13023</v>
+        <v>-13023</v>
       </c>
       <c r="E13" s="17">
-        <v>13024</v>
+        <v>-13024</v>
       </c>
       <c r="F13" s="17">
-        <v>13025</v>
+        <v>-13025</v>
       </c>
       <c r="G13" s="17">
-        <v>13026</v>
+        <v>-13026</v>
       </c>
       <c r="H13" s="17">
-        <v>13027</v>
+        <v>-13027</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22985,22 +22985,22 @@
         <v>1961</v>
       </c>
       <c r="C14" s="17">
-        <v>13028</v>
+        <v>-13028</v>
       </c>
       <c r="D14" s="17">
-        <v>13029</v>
+        <v>-13029</v>
       </c>
       <c r="E14" s="17">
-        <v>13030</v>
+        <v>-13030</v>
       </c>
       <c r="F14" s="17">
-        <v>13031</v>
+        <v>-13031</v>
       </c>
       <c r="G14" s="17">
-        <v>13032</v>
+        <v>-13032</v>
       </c>
       <c r="H14" s="17">
-        <v>13033</v>
+        <v>-13033</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23026,10 +23026,10 @@
         <v>13037</v>
       </c>
       <c r="G16" s="17">
-        <v>13038</v>
+        <v>-13038</v>
       </c>
       <c r="H16" s="17">
-        <v>13039</v>
+        <v>-13039</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23052,10 +23052,10 @@
         <v>13043</v>
       </c>
       <c r="G17" s="17">
-        <v>13044</v>
+        <v>-13044</v>
       </c>
       <c r="H17" s="17">
-        <v>13045</v>
+        <v>-13045</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23078,10 +23078,10 @@
         <v>13049</v>
       </c>
       <c r="G18" s="17">
-        <v>13050</v>
+        <v>-13050</v>
       </c>
       <c r="H18" s="17">
-        <v>13051</v>
+        <v>-13051</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23104,10 +23104,10 @@
         <v>13061</v>
       </c>
       <c r="G19" s="17">
-        <v>13062</v>
+        <v>-13062</v>
       </c>
       <c r="H19" s="17">
-        <v>13063</v>
+        <v>-13063</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23130,10 +23130,10 @@
         <v>13067</v>
       </c>
       <c r="G20" s="17">
-        <v>13068</v>
+        <v>-13068</v>
       </c>
       <c r="H20" s="17">
-        <v>13069</v>
+        <v>-13069</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23156,10 +23156,10 @@
         <v>13073</v>
       </c>
       <c r="G21" s="17">
-        <v>13074</v>
+        <v>-13074</v>
       </c>
       <c r="H21" s="17">
-        <v>13075</v>
+        <v>-13075</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23170,22 +23170,22 @@
         <v>1947</v>
       </c>
       <c r="C22" s="17">
-        <v>13076</v>
+        <v>-13076</v>
       </c>
       <c r="D22" s="17">
-        <v>13077</v>
+        <v>-13077</v>
       </c>
       <c r="E22" s="17">
-        <v>13078</v>
+        <v>-13078</v>
       </c>
       <c r="F22" s="17">
-        <v>13079</v>
+        <v>-13079</v>
       </c>
       <c r="G22" s="17">
-        <v>13080</v>
+        <v>-13080</v>
       </c>
       <c r="H22" s="17">
-        <v>13081</v>
+        <v>-13081</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23208,10 +23208,10 @@
         <v>13085</v>
       </c>
       <c r="G23" s="17">
-        <v>13086</v>
+        <v>-13086</v>
       </c>
       <c r="H23" s="17">
-        <v>13087</v>
+        <v>-13087</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23234,10 +23234,10 @@
         <v>13091</v>
       </c>
       <c r="G24" s="17">
-        <v>13092</v>
+        <v>-13092</v>
       </c>
       <c r="H24" s="17">
-        <v>13093</v>
+        <v>-13093</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,22 +23248,22 @@
         <v>1941</v>
       </c>
       <c r="C25" s="17">
-        <v>13094</v>
+        <v>-13094</v>
       </c>
       <c r="D25" s="17">
-        <v>13095</v>
+        <v>-13095</v>
       </c>
       <c r="E25" s="17">
-        <v>13096</v>
+        <v>-13096</v>
       </c>
       <c r="F25" s="17">
-        <v>13097</v>
+        <v>-13097</v>
       </c>
       <c r="G25" s="17">
-        <v>13098</v>
+        <v>-13098</v>
       </c>
       <c r="H25" s="17">
-        <v>13099</v>
+        <v>-13099</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23277,22 +23277,22 @@
         <v>1939</v>
       </c>
       <c r="C27" s="17">
-        <v>13100</v>
+        <v>-13100</v>
       </c>
       <c r="D27" s="17">
-        <v>13101</v>
+        <v>-13101</v>
       </c>
       <c r="E27" s="17">
-        <v>13102</v>
+        <v>-13102</v>
       </c>
       <c r="F27" s="17">
-        <v>13103</v>
+        <v>-13103</v>
       </c>
       <c r="G27" s="17">
-        <v>13104</v>
+        <v>-13104</v>
       </c>
       <c r="H27" s="17">
-        <v>13105</v>
+        <v>-13105</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23328,7 +23328,7 @@
         <v>1933</v>
       </c>
       <c r="G31" s="17">
-        <v>13108</v>
+        <v>-13108</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23356,22 +23356,22 @@
         <v>1930</v>
       </c>
       <c r="C35" s="17">
-        <v>13110</v>
+        <v>-13110</v>
       </c>
       <c r="D35" s="17">
-        <v>13111</v>
+        <v>-13111</v>
       </c>
       <c r="E35" s="17">
-        <v>13112</v>
+        <v>-13112</v>
       </c>
       <c r="F35" s="17">
-        <v>13113</v>
+        <v>-13113</v>
       </c>
       <c r="G35" s="17">
-        <v>13114</v>
+        <v>-13114</v>
       </c>
       <c r="H35" s="17">
-        <v>13115</v>
+        <v>-13115</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23407,7 +23407,7 @@
         <v>13117</v>
       </c>
       <c r="G39" s="17">
-        <v>13118</v>
+        <v>-13118</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23424,7 +23424,7 @@
         <v>13120</v>
       </c>
       <c r="G40" s="17">
-        <v>13121</v>
+        <v>-13121</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23441,7 +23441,7 @@
         <v>13123</v>
       </c>
       <c r="G41" s="17">
-        <v>13124</v>
+        <v>-13124</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23458,7 +23458,7 @@
         <v>13126</v>
       </c>
       <c r="G42" s="17">
-        <v>13127</v>
+        <v>-13127</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23475,7 +23475,7 @@
         <v>13129</v>
       </c>
       <c r="G43" s="17">
-        <v>13130</v>
+        <v>-13130</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23489,7 +23489,7 @@
         <v>13131</v>
       </c>
       <c r="G44" s="17">
-        <v>13132</v>
+        <v>-13132</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23503,7 +23503,7 @@
         <v>13133</v>
       </c>
       <c r="G45" s="17">
-        <v>13134</v>
+        <v>-13134</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23517,7 +23517,7 @@
         <v>13135</v>
       </c>
       <c r="G46" s="17">
-        <v>13136</v>
+        <v>-13136</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23531,13 +23531,13 @@
         <v>1915</v>
       </c>
       <c r="D48" s="17">
-        <v>13137</v>
+        <v>-13137</v>
       </c>
       <c r="E48" s="17">
-        <v>13138</v>
+        <v>-13138</v>
       </c>
       <c r="G48" s="17">
-        <v>13139</v>
+        <v>-13139</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23583,7 +23583,7 @@
         <v>154</v>
       </c>
       <c r="G54" s="17">
-        <v>13142</v>
+        <v>-13142</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23597,19 +23597,19 @@
         <v>1910</v>
       </c>
       <c r="C56" s="17">
-        <v>13143</v>
+        <v>-13143</v>
       </c>
       <c r="D56" s="17">
-        <v>13144</v>
+        <v>-13144</v>
       </c>
       <c r="E56" s="17">
-        <v>13145</v>
+        <v>-13145</v>
       </c>
       <c r="F56" s="17">
-        <v>13146</v>
+        <v>-13146</v>
       </c>
       <c r="G56" s="17">
-        <v>13147</v>
+        <v>-13147</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23691,7 +23691,7 @@
         <v>171</v>
       </c>
       <c r="G66" s="17">
-        <v>13153</v>
+        <v>-13153</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23705,7 +23705,7 @@
         <v>173</v>
       </c>
       <c r="G68" s="17">
-        <v>13154</v>
+        <v>-13154</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23828,7 +23828,7 @@
         <v>198</v>
       </c>
       <c r="G81" s="17">
-        <v>13164</v>
+        <v>-13164</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23842,7 +23842,7 @@
         <v>200</v>
       </c>
       <c r="G83" s="17">
-        <v>13165</v>
+        <v>-13165</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23997,10 +23997,10 @@
         <v>1875</v>
       </c>
       <c r="C98" s="17">
-        <v>13182</v>
+        <v>-13182</v>
       </c>
       <c r="G98" s="17">
-        <v>13183</v>
+        <v>-13183</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24077,7 +24077,7 @@
         <v>1864</v>
       </c>
       <c r="C107" s="17">
-        <v>13190</v>
+        <v>-13190</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/GRID_TO_LOAD.xlsx
+++ b/GRID_TO_LOAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhino\Documents\PROJEKTS JS\Mapping is boring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D97596-A314-41D5-9E2E-7968955A1168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972B056B-F1C6-4E7D-8773-E641AE92BAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="13" xr2:uid="{B34349A9-D588-42E5-9EA3-3BAC4BC5A281}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="18" xr2:uid="{B34349A9-D588-42E5-9EA3-3BAC4BC5A281}"/>
   </bookViews>
   <sheets>
     <sheet name="VN Alfa Romeo" sheetId="13" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5579" uniqueCount="2657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5580" uniqueCount="2658">
   <si>
     <t>Ventes Véhicules Neufs - Citroën VP</t>
   </si>
@@ -8030,6 +8030,9 @@
   </si>
   <si>
     <t>LEAPMOTOR</t>
+  </si>
+  <si>
+    <t>+27378</t>
   </si>
 </sst>
 </file>
@@ -8135,7 +8138,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -8201,6 +8204,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -32192,8 +32198,8 @@
       <c r="B79" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="C79" s="15">
-        <v>27378</v>
+      <c r="C79" s="24" t="s">
+        <v>2657</v>
       </c>
       <c r="D79" s="15">
         <v>27379</v>

--- a/GRID_TO_LOAD.xlsx
+++ b/GRID_TO_LOAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhino\Documents\PROJEKTS JS\Mapping is boring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD188F7-4B51-461B-8853-AAA26DC52FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32251B46-FD46-4011-9F57-A0BE9A317EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="20" xr2:uid="{B34349A9-D588-42E5-9EA3-3BAC4BC5A281}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="18" xr2:uid="{B34349A9-D588-42E5-9EA3-3BAC4BC5A281}"/>
   </bookViews>
   <sheets>
     <sheet name="VN Alfa Romeo" sheetId="13" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5533" uniqueCount="2658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5518" uniqueCount="2657">
   <si>
     <t>Ventes Véhicules Neufs - Citroën VP</t>
   </si>
@@ -8030,15 +8030,15 @@
   </si>
   <si>
     <t>LEAPMOTOR</t>
-  </si>
-  <si>
-    <t>+27378</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\+#"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -8205,7 +8205,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -22016,7 +22016,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1359B-2BED-4443-9FE8-FE347FB52A60}">
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="9" customWidth="1"/>
@@ -22026,12 +22026,11 @@
     <col min="5" max="5" width="15.88671875" style="9" customWidth="1"/>
     <col min="6" max="6" width="19.5546875" style="9" customWidth="1"/>
     <col min="7" max="7" width="14.44140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="9" customWidth="1"/>
-    <col min="9" max="256" width="9.109375" style="9" customWidth="1"/>
-    <col min="257" max="16384" width="11.44140625" style="9"/>
+    <col min="8" max="255" width="9.109375" style="9" customWidth="1"/>
+    <col min="256" max="16384" width="11.44140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>2631</v>
       </c>
@@ -22053,11 +22052,8 @@
       <c r="G1" s="23" t="s">
         <v>2639</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>0</v>
       </c>
@@ -22079,19 +22075,16 @@
       <c r="G2" s="23">
         <v>100</v>
       </c>
-      <c r="H2" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
     </row>
-    <row r="5" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="13" t="s">
         <v>2</v>
       </c>
@@ -22107,11 +22100,8 @@
       <c r="G5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>1978</v>
       </c>
@@ -22133,11 +22123,8 @@
       <c r="G6" s="17">
         <v>-12978</v>
       </c>
-      <c r="H6" s="17">
-        <v>-12979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>1976</v>
       </c>
@@ -22159,11 +22146,8 @@
       <c r="G7" s="17">
         <v>-12984</v>
       </c>
-      <c r="H7" s="17">
-        <v>-12985</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>1974</v>
       </c>
@@ -22185,11 +22169,8 @@
       <c r="G8" s="17">
         <v>-12990</v>
       </c>
-      <c r="H8" s="17">
-        <v>-12991</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>1972</v>
       </c>
@@ -22211,11 +22192,8 @@
       <c r="G9" s="17">
         <v>-12996</v>
       </c>
-      <c r="H9" s="17">
-        <v>-12997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>1970</v>
       </c>
@@ -22237,11 +22215,8 @@
       <c r="G10" s="17">
         <v>-13008</v>
       </c>
-      <c r="H10" s="17">
-        <v>-13009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>1968</v>
       </c>
@@ -22263,11 +22238,8 @@
       <c r="G11" s="17">
         <v>-13014</v>
       </c>
-      <c r="H11" s="17">
-        <v>-13015</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>1966</v>
       </c>
@@ -22289,11 +22261,8 @@
       <c r="G12" s="17">
         <v>-13020</v>
       </c>
-      <c r="H12" s="17">
-        <v>-13021</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>1964</v>
       </c>
@@ -22315,11 +22284,8 @@
       <c r="G13" s="17">
         <v>-13026</v>
       </c>
-      <c r="H13" s="17">
-        <v>-13027</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>1962</v>
       </c>
@@ -22341,14 +22307,11 @@
       <c r="G14" s="17">
         <v>-13032</v>
       </c>
-      <c r="H14" s="17">
-        <v>-13033</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
     </row>
-    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>1960</v>
       </c>
@@ -22370,11 +22333,8 @@
       <c r="G16" s="17">
         <v>-13038</v>
       </c>
-      <c r="H16" s="17">
-        <v>-13039</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>1958</v>
       </c>
@@ -22396,11 +22356,8 @@
       <c r="G17" s="17">
         <v>-13044</v>
       </c>
-      <c r="H17" s="17">
-        <v>-13045</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>1956</v>
       </c>
@@ -22422,11 +22379,8 @@
       <c r="G18" s="17">
         <v>-13050</v>
       </c>
-      <c r="H18" s="17">
-        <v>-13051</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>1954</v>
       </c>
@@ -22448,11 +22402,8 @@
       <c r="G19" s="17">
         <v>-13062</v>
       </c>
-      <c r="H19" s="17">
-        <v>-13063</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>1952</v>
       </c>
@@ -22474,11 +22425,8 @@
       <c r="G20" s="17">
         <v>-13068</v>
       </c>
-      <c r="H20" s="17">
-        <v>-13069</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>1950</v>
       </c>
@@ -22500,11 +22448,8 @@
       <c r="G21" s="17">
         <v>-13074</v>
       </c>
-      <c r="H21" s="17">
-        <v>-13075</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>1948</v>
       </c>
@@ -22526,11 +22471,8 @@
       <c r="G22" s="17">
         <v>-13080</v>
       </c>
-      <c r="H22" s="17">
-        <v>-13081</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>1946</v>
       </c>
@@ -22552,11 +22494,8 @@
       <c r="G23" s="17">
         <v>-13086</v>
       </c>
-      <c r="H23" s="17">
-        <v>-13087</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>1944</v>
       </c>
@@ -22578,11 +22517,8 @@
       <c r="G24" s="17">
         <v>-13092</v>
       </c>
-      <c r="H24" s="17">
-        <v>-13093</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>1942</v>
       </c>
@@ -22604,14 +22540,11 @@
       <c r="G25" s="17">
         <v>-13098</v>
       </c>
-      <c r="H25" s="17">
-        <v>-13099</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
     </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>1940</v>
       </c>
@@ -22633,14 +22566,11 @@
       <c r="G27" s="17">
         <v>-13104</v>
       </c>
-      <c r="H27" s="17">
-        <v>-13105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
     </row>
-    <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>1938</v>
       </c>
@@ -22651,7 +22581,7 @@
         <v>13106</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>1936</v>
       </c>
@@ -22662,7 +22592,7 @@
         <v>13107</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>1934</v>
       </c>
@@ -22673,10 +22603,10 @@
         <v>-13108</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
     </row>
-    <row r="33" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>1932</v>
       </c>
@@ -22687,10 +22617,10 @@
         <v>13109</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
     </row>
-    <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>1931</v>
       </c>
@@ -22712,19 +22642,16 @@
       <c r="G35" s="17">
         <v>-13114</v>
       </c>
-      <c r="H35" s="17">
-        <v>-13115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
     </row>
-    <row r="37" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="12" t="s">
         <v>1929</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="13" t="s">
         <v>5</v>
       </c>
@@ -22735,7 +22662,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>1928</v>
       </c>
@@ -22752,7 +22679,7 @@
         <v>-13118</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>1927</v>
       </c>
@@ -22769,7 +22696,7 @@
         <v>-13121</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>1925</v>
       </c>
@@ -22786,7 +22713,7 @@
         <v>-13124</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>1923</v>
       </c>
@@ -22803,7 +22730,7 @@
         <v>-13127</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>1922</v>
       </c>
@@ -22820,7 +22747,7 @@
         <v>-13130</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>1921</v>
       </c>
@@ -22834,7 +22761,7 @@
         <v>-13132</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>1920</v>
       </c>
@@ -22848,7 +22775,7 @@
         <v>-13134</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>1918</v>
       </c>
@@ -22862,10 +22789,10 @@
         <v>-13136</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
     </row>
-    <row r="48" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>1916</v>
       </c>
@@ -24820,7 +24747,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA03963-472F-460A-B030-565465DF6A9A}">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="9" customWidth="1"/>
@@ -24831,12 +24758,11 @@
     <col min="6" max="6" width="12.44140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" style="9" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="16" style="9" customWidth="1"/>
-    <col min="10" max="256" width="9.109375" style="9" customWidth="1"/>
-    <col min="257" max="16384" width="11.44140625" style="9"/>
+    <col min="9" max="255" width="9.109375" style="9" customWidth="1"/>
+    <col min="256" max="16384" width="11.44140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>2631</v>
       </c>
@@ -24861,11 +24787,8 @@
       <c r="H1" s="23" t="s">
         <v>2639</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>0</v>
       </c>
@@ -24890,24 +24813,21 @@
       <c r="H2" s="23">
         <v>100</v>
       </c>
-      <c r="I2" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>2171</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
     </row>
-    <row r="5" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>2170</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="13" t="s">
         <v>2058</v>
       </c>
@@ -24926,11 +24846,8 @@
       <c r="H6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>2169</v>
       </c>
@@ -24955,11 +24872,8 @@
       <c r="H7" s="17">
         <v>-16467</v>
       </c>
-      <c r="I7" s="17">
-        <v>-16468</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>2168</v>
       </c>
@@ -24984,11 +24898,8 @@
       <c r="H8" s="17">
         <v>-16474</v>
       </c>
-      <c r="I8" s="17">
-        <v>-16475</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>2167</v>
       </c>
@@ -25013,11 +24924,8 @@
       <c r="H9" s="17">
         <v>-16481</v>
       </c>
-      <c r="I9" s="17">
-        <v>-16482</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>2166</v>
       </c>
@@ -25042,11 +24950,8 @@
       <c r="H10" s="17">
         <v>-16495</v>
       </c>
-      <c r="I10" s="17">
-        <v>-16496</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>2165</v>
       </c>
@@ -25071,11 +24976,8 @@
       <c r="H11" s="17">
         <v>-16502</v>
       </c>
-      <c r="I11" s="17">
-        <v>-16503</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>2164</v>
       </c>
@@ -25100,14 +25002,11 @@
       <c r="H12" s="17">
         <v>-16516</v>
       </c>
-      <c r="I12" s="17">
-        <v>-16517</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
     </row>
-    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>2163</v>
       </c>
@@ -25132,11 +25031,8 @@
       <c r="H14" s="17">
         <v>-16523</v>
       </c>
-      <c r="I14" s="17">
-        <v>-16524</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>2162</v>
       </c>
@@ -25161,11 +25057,8 @@
       <c r="H15" s="17">
         <v>-16530</v>
       </c>
-      <c r="I15" s="17">
-        <v>-16531</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>2161</v>
       </c>
@@ -25190,11 +25083,8 @@
       <c r="H16" s="17">
         <v>-16537</v>
       </c>
-      <c r="I16" s="17">
-        <v>-16538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>2160</v>
       </c>
@@ -25219,11 +25109,8 @@
       <c r="H17" s="17">
         <v>-16551</v>
       </c>
-      <c r="I17" s="17">
-        <v>-16552</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>2159</v>
       </c>
@@ -25248,11 +25135,8 @@
       <c r="H18" s="17">
         <v>-16558</v>
       </c>
-      <c r="I18" s="17">
-        <v>-16559</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>2158</v>
       </c>
@@ -25277,19 +25161,16 @@
       <c r="H19" s="17">
         <v>-16572</v>
       </c>
-      <c r="I19" s="17">
-        <v>-16573</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
     </row>
-    <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H21" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>2156</v>
       </c>
@@ -25300,7 +25181,7 @@
         <v>16574</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>2155</v>
       </c>
@@ -25311,7 +25192,7 @@
         <v>16575</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>2154</v>
       </c>
@@ -25322,7 +25203,7 @@
         <v>16576</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>2153</v>
       </c>
@@ -25333,10 +25214,10 @@
         <v>-16577</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
     </row>
-    <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F27" s="13" t="s">
         <v>5</v>
       </c>
@@ -25347,7 +25228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>2151</v>
       </c>
@@ -25364,7 +25245,7 @@
         <v>-16580</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>2149</v>
       </c>
@@ -25381,7 +25262,7 @@
         <v>-16583</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>2147</v>
       </c>
@@ -25398,10 +25279,10 @@
         <v>-16589</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
     </row>
-    <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F32" s="13" t="s">
         <v>5</v>
       </c>
@@ -25895,7 +25776,7 @@
         <v>16641</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
         <v>2079</v>
       </c>
@@ -25906,7 +25787,7 @@
         <v>16642</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>2077</v>
       </c>
@@ -25917,7 +25798,7 @@
         <v>16643</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
         <v>2075</v>
       </c>
@@ -25928,7 +25809,7 @@
         <v>16645</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>2073</v>
       </c>
@@ -25939,7 +25820,7 @@
         <v>16646</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
         <v>2071</v>
       </c>
@@ -25950,20 +25831,20 @@
         <v>-16648</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11"/>
     </row>
-    <row r="87" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="12" t="s">
         <v>2069</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
         <v>2068</v>
       </c>
@@ -25974,7 +25855,7 @@
         <v>16649</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
         <v>2067</v>
       </c>
@@ -25985,7 +25866,7 @@
         <v>16650</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>2065</v>
       </c>
@@ -25996,7 +25877,7 @@
         <v>16651</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
         <v>2063</v>
       </c>
@@ -26007,7 +25888,7 @@
         <v>16653</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
         <v>2061</v>
       </c>
@@ -26018,15 +25899,15 @@
         <v>16654</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11"/>
     </row>
-    <row r="95" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="12" t="s">
         <v>2059</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="13" t="s">
         <v>2058</v>
       </c>
@@ -26045,11 +25926,8 @@
       <c r="H96" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
         <v>2056</v>
       </c>
@@ -26074,11 +25952,8 @@
       <c r="H97" s="17">
         <v>-16661</v>
       </c>
-      <c r="I97" s="17">
-        <v>-16662</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
         <v>2054</v>
       </c>
@@ -26102,9 +25977,6 @@
       </c>
       <c r="H98" s="17">
         <v>-16668</v>
-      </c>
-      <c r="I98" s="17">
-        <v>-16669</v>
       </c>
     </row>
   </sheetData>
@@ -26116,7 +25988,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA671AA3-DBD3-458F-AB2B-34AEE8727175}">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="9" customWidth="1"/>
@@ -26127,12 +25999,11 @@
     <col min="6" max="6" width="12.44140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="16.44140625" style="9" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" style="9" customWidth="1"/>
-    <col min="10" max="256" width="9.109375" style="9" customWidth="1"/>
-    <col min="257" max="16384" width="11.44140625" style="9"/>
+    <col min="9" max="255" width="9.109375" style="9" customWidth="1"/>
+    <col min="256" max="16384" width="11.44140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>2631</v>
       </c>
@@ -26157,11 +26028,8 @@
       <c r="H1" s="23" t="s">
         <v>2639</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>0</v>
       </c>
@@ -26186,24 +26054,21 @@
       <c r="H2" s="23">
         <v>100</v>
       </c>
-      <c r="I2" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>2172</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
     </row>
-    <row r="5" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>2170</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="13" t="s">
         <v>2058</v>
       </c>
@@ -26222,11 +26087,8 @@
       <c r="H6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>2173</v>
       </c>
@@ -26251,11 +26113,8 @@
       <c r="H7" s="17">
         <v>-17091</v>
       </c>
-      <c r="I7" s="17">
-        <v>-17092</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>2174</v>
       </c>
@@ -26280,11 +26139,8 @@
       <c r="H8" s="17">
         <v>-17098</v>
       </c>
-      <c r="I8" s="17">
-        <v>-17099</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>2175</v>
       </c>
@@ -26309,11 +26165,8 @@
       <c r="H9" s="17">
         <v>-17105</v>
       </c>
-      <c r="I9" s="17">
-        <v>-17106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>2176</v>
       </c>
@@ -26338,11 +26191,8 @@
       <c r="H10" s="17">
         <v>-17119</v>
       </c>
-      <c r="I10" s="17">
-        <v>-17120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>2177</v>
       </c>
@@ -26367,11 +26217,8 @@
       <c r="H11" s="17">
         <v>-17126</v>
       </c>
-      <c r="I11" s="17">
-        <v>-17127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>2178</v>
       </c>
@@ -26396,14 +26243,11 @@
       <c r="H12" s="17">
         <v>-17140</v>
       </c>
-      <c r="I12" s="17">
-        <v>-17141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
     </row>
-    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>2180</v>
       </c>
@@ -26428,11 +26272,8 @@
       <c r="H14" s="17">
         <v>-17147</v>
       </c>
-      <c r="I14" s="17">
-        <v>-17148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>2181</v>
       </c>
@@ -26457,11 +26298,8 @@
       <c r="H15" s="17">
         <v>-17154</v>
       </c>
-      <c r="I15" s="17">
-        <v>-17155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>2182</v>
       </c>
@@ -26486,11 +26324,8 @@
       <c r="H16" s="17">
         <v>-17161</v>
       </c>
-      <c r="I16" s="17">
-        <v>-17162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>2183</v>
       </c>
@@ -26515,11 +26350,8 @@
       <c r="H17" s="17">
         <v>-17175</v>
       </c>
-      <c r="I17" s="17">
-        <v>-17176</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>2184</v>
       </c>
@@ -26544,11 +26376,8 @@
       <c r="H18" s="17">
         <v>-17182</v>
       </c>
-      <c r="I18" s="17">
-        <v>-17183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>2185</v>
       </c>
@@ -26573,19 +26402,16 @@
       <c r="H19" s="17">
         <v>-17196</v>
       </c>
-      <c r="I19" s="17">
-        <v>-17197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
     </row>
-    <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H21" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>2186</v>
       </c>
@@ -26596,7 +26422,7 @@
         <v>17198</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>2187</v>
       </c>
@@ -26607,7 +26433,7 @@
         <v>17199</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>2188</v>
       </c>
@@ -26618,7 +26444,7 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>2189</v>
       </c>
@@ -26629,10 +26455,10 @@
         <v>-17201</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
     </row>
-    <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F27" s="13" t="s">
         <v>5</v>
       </c>
@@ -26643,7 +26469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>2190</v>
       </c>
@@ -26660,7 +26486,7 @@
         <v>-17204</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>2191</v>
       </c>
@@ -26677,7 +26503,7 @@
         <v>-17207</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>2192</v>
       </c>
@@ -26694,10 +26520,10 @@
         <v>-17213</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
     </row>
-    <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F32" s="13" t="s">
         <v>5</v>
       </c>
@@ -27191,7 +27017,7 @@
         <v>17265</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
         <v>2229</v>
       </c>
@@ -27202,7 +27028,7 @@
         <v>17266</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>2230</v>
       </c>
@@ -27213,7 +27039,7 @@
         <v>17267</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
         <v>2231</v>
       </c>
@@ -27224,7 +27050,7 @@
         <v>17269</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>2232</v>
       </c>
@@ -27235,7 +27061,7 @@
         <v>17270</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
         <v>2233</v>
       </c>
@@ -27246,20 +27072,20 @@
         <v>-17272</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11"/>
     </row>
-    <row r="87" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="12" t="s">
         <v>2069</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
         <v>2234</v>
       </c>
@@ -27270,7 +27096,7 @@
         <v>17273</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
         <v>2235</v>
       </c>
@@ -27281,7 +27107,7 @@
         <v>17274</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>2236</v>
       </c>
@@ -27292,7 +27118,7 @@
         <v>17275</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
         <v>2237</v>
       </c>
@@ -27303,7 +27129,7 @@
         <v>17277</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
         <v>2238</v>
       </c>
@@ -27314,15 +27140,15 @@
         <v>17278</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11"/>
     </row>
-    <row r="95" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="12" t="s">
         <v>2059</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="13" t="s">
         <v>2058</v>
       </c>
@@ -27341,11 +27167,8 @@
       <c r="H96" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
         <v>2239</v>
       </c>
@@ -27370,11 +27193,8 @@
       <c r="H97" s="17">
         <v>-17285</v>
       </c>
-      <c r="I97" s="17">
-        <v>-17286</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
         <v>2240</v>
       </c>
@@ -27398,9 +27218,6 @@
       </c>
       <c r="H98" s="17">
         <v>-17292</v>
-      </c>
-      <c r="I98" s="17">
-        <v>-17293</v>
       </c>
     </row>
   </sheetData>
@@ -27412,7 +27229,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7630DE-CC69-47D5-A878-F79B7E735239}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="9" customWidth="1"/>
@@ -27422,12 +27239,11 @@
     <col min="5" max="5" width="12.44140625" style="9" customWidth="1"/>
     <col min="6" max="6" width="15.44140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="14.44140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="9" customWidth="1"/>
-    <col min="9" max="256" width="9.109375" style="9" customWidth="1"/>
-    <col min="257" max="16384" width="11.44140625" style="9"/>
+    <col min="8" max="255" width="9.109375" style="9" customWidth="1"/>
+    <col min="256" max="16384" width="11.44140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>2631</v>
       </c>
@@ -27449,11 +27265,8 @@
       <c r="G1" s="23" t="s">
         <v>2639</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>0</v>
       </c>
@@ -27475,24 +27288,21 @@
       <c r="G2" s="23">
         <v>100</v>
       </c>
-      <c r="H2" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>2241</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
     </row>
-    <row r="5" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>2242</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="13" t="s">
         <v>2057</v>
       </c>
@@ -27508,11 +27318,8 @@
       <c r="G6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>2243</v>
       </c>
@@ -27534,11 +27341,8 @@
       <c r="G7" s="17">
         <v>-19968</v>
       </c>
-      <c r="H7" s="17">
-        <v>-19969</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>2245</v>
       </c>
@@ -27560,11 +27364,8 @@
       <c r="G8" s="17">
         <v>-19974</v>
       </c>
-      <c r="H8" s="17">
-        <v>-19975</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>2247</v>
       </c>
@@ -27586,11 +27387,8 @@
       <c r="G9" s="17">
         <v>-19980</v>
       </c>
-      <c r="H9" s="17">
-        <v>-19981</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>2249</v>
       </c>
@@ -27612,11 +27410,8 @@
       <c r="G10" s="17">
         <v>-19986</v>
       </c>
-      <c r="H10" s="17">
-        <v>-19987</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>2251</v>
       </c>
@@ -27638,11 +27433,8 @@
       <c r="G11" s="17">
         <v>-19998</v>
       </c>
-      <c r="H11" s="17">
-        <v>-19999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>2253</v>
       </c>
@@ -27664,11 +27456,8 @@
       <c r="G12" s="17">
         <v>-20004</v>
       </c>
-      <c r="H12" s="17">
-        <v>-20005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>2254</v>
       </c>
@@ -27690,14 +27479,11 @@
       <c r="G13" s="17">
         <v>-20010</v>
       </c>
-      <c r="H13" s="17">
-        <v>-20011</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
     </row>
-    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>2256</v>
       </c>
@@ -27719,11 +27505,8 @@
       <c r="G15" s="17">
         <v>-20016</v>
       </c>
-      <c r="H15" s="17">
-        <v>-20017</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>2257</v>
       </c>
@@ -27745,11 +27528,8 @@
       <c r="G16" s="17">
         <v>-20022</v>
       </c>
-      <c r="H16" s="17">
-        <v>-20023</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>2258</v>
       </c>
@@ -27771,11 +27551,8 @@
       <c r="G17" s="17">
         <v>-20028</v>
       </c>
-      <c r="H17" s="17">
-        <v>-20029</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>2259</v>
       </c>
@@ -27797,11 +27574,8 @@
       <c r="G18" s="17">
         <v>-20034</v>
       </c>
-      <c r="H18" s="17">
-        <v>-20035</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>2260</v>
       </c>
@@ -27823,11 +27597,8 @@
       <c r="G19" s="17">
         <v>-20046</v>
       </c>
-      <c r="H19" s="17">
-        <v>-20047</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>2261</v>
       </c>
@@ -27849,11 +27620,8 @@
       <c r="G20" s="17">
         <v>-20052</v>
       </c>
-      <c r="H20" s="17">
-        <v>-20053</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>2262</v>
       </c>
@@ -27875,14 +27643,11 @@
       <c r="G21" s="17">
         <v>-20058</v>
       </c>
-      <c r="H21" s="17">
-        <v>-20059</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
     </row>
-    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>2263</v>
       </c>
@@ -27904,11 +27669,8 @@
       <c r="G23" s="17">
         <v>-20064</v>
       </c>
-      <c r="H23" s="17">
-        <v>-20065</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>2265</v>
       </c>
@@ -27930,11 +27692,8 @@
       <c r="G24" s="17">
         <v>-20070</v>
       </c>
-      <c r="H24" s="17">
-        <v>-20071</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>2267</v>
       </c>
@@ -27956,11 +27715,8 @@
       <c r="G25" s="17">
         <v>-20076</v>
       </c>
-      <c r="H25" s="17">
-        <v>-20077</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>2269</v>
       </c>
@@ -27982,11 +27738,8 @@
       <c r="G26" s="17">
         <v>-20088</v>
       </c>
-      <c r="H26" s="17">
-        <v>-20089</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>2271</v>
       </c>
@@ -28008,11 +27761,8 @@
       <c r="G27" s="17">
         <v>-20094</v>
       </c>
-      <c r="H27" s="17">
-        <v>-20095</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>2273</v>
       </c>
@@ -28034,11 +27784,8 @@
       <c r="G28" s="17">
         <v>-20100</v>
       </c>
-      <c r="H28" s="17">
-        <v>-20101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>2275</v>
       </c>
@@ -28060,14 +27807,11 @@
       <c r="G29" s="17">
         <v>-20106</v>
       </c>
-      <c r="H29" s="17">
-        <v>-20107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
     </row>
-    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>2277</v>
       </c>
@@ -28089,11 +27833,8 @@
       <c r="G31" s="17">
         <v>-20112</v>
       </c>
-      <c r="H31" s="17">
-        <v>-20113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>2278</v>
       </c>
@@ -28115,11 +27856,8 @@
       <c r="G32" s="17">
         <v>-20118</v>
       </c>
-      <c r="H32" s="17">
-        <v>-20119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>2279</v>
       </c>
@@ -28141,11 +27879,8 @@
       <c r="G33" s="17">
         <v>-20124</v>
       </c>
-      <c r="H33" s="17">
-        <v>-20125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>2280</v>
       </c>
@@ -28167,11 +27902,8 @@
       <c r="G34" s="17">
         <v>-20136</v>
       </c>
-      <c r="H34" s="17">
-        <v>-20137</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>2281</v>
       </c>
@@ -28193,11 +27925,8 @@
       <c r="G35" s="17">
         <v>-20142</v>
       </c>
-      <c r="H35" s="17">
-        <v>-20143</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>2282</v>
       </c>
@@ -28219,11 +27948,8 @@
       <c r="G36" s="17">
         <v>-20148</v>
       </c>
-      <c r="H36" s="17">
-        <v>-20149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>2283</v>
       </c>
@@ -28245,14 +27971,11 @@
       <c r="G37" s="17">
         <v>-20154</v>
       </c>
-      <c r="H37" s="17">
-        <v>-20155</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
     </row>
-    <row r="39" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>2284</v>
       </c>
@@ -28274,11 +27997,8 @@
       <c r="G39" s="17">
         <v>-20160</v>
       </c>
-      <c r="H39" s="17">
-        <v>-20161</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>2286</v>
       </c>
@@ -28300,11 +28020,8 @@
       <c r="G40" s="17">
         <v>-20166</v>
       </c>
-      <c r="H40" s="17">
-        <v>-20167</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>2288</v>
       </c>
@@ -28326,11 +28043,8 @@
       <c r="G41" s="17">
         <v>-20178</v>
       </c>
-      <c r="H41" s="17">
-        <v>-20179</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>2290</v>
       </c>
@@ -28352,11 +28066,8 @@
       <c r="G42" s="17">
         <v>-20184</v>
       </c>
-      <c r="H42" s="17">
-        <v>-20185</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>2292</v>
       </c>
@@ -28378,14 +28089,11 @@
       <c r="G43" s="17">
         <v>-20190</v>
       </c>
-      <c r="H43" s="17">
-        <v>-20191</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
     </row>
-    <row r="45" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>2294</v>
       </c>
@@ -28407,11 +28115,8 @@
       <c r="G45" s="17">
         <v>-20196</v>
       </c>
-      <c r="H45" s="17">
-        <v>-20197</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>2295</v>
       </c>
@@ -28433,11 +28138,8 @@
       <c r="G46" s="17">
         <v>-20202</v>
       </c>
-      <c r="H46" s="17">
-        <v>-20203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>2296</v>
       </c>
@@ -28459,11 +28161,8 @@
       <c r="G47" s="17">
         <v>-20214</v>
       </c>
-      <c r="H47" s="17">
-        <v>-20215</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>2297</v>
       </c>
@@ -28485,11 +28184,8 @@
       <c r="G48" s="17">
         <v>-20220</v>
       </c>
-      <c r="H48" s="17">
-        <v>-20221</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
         <v>2298</v>
       </c>
@@ -28511,14 +28207,11 @@
       <c r="G49" s="17">
         <v>-20226</v>
       </c>
-      <c r="H49" s="17">
-        <v>-20227</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
     </row>
-    <row r="51" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>2299</v>
       </c>
@@ -28540,11 +28233,8 @@
       <c r="G51" s="17">
         <v>-20232</v>
       </c>
-      <c r="H51" s="17">
-        <v>-20233</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>2301</v>
       </c>
@@ -28566,11 +28256,8 @@
       <c r="G52" s="17">
         <v>-20238</v>
       </c>
-      <c r="H52" s="17">
-        <v>-20239</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>2302</v>
       </c>
@@ -28592,14 +28279,11 @@
       <c r="G53" s="17">
         <v>-20244</v>
       </c>
-      <c r="H53" s="17">
-        <v>-20245</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
     </row>
-    <row r="55" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>2304</v>
       </c>
@@ -28621,14 +28305,11 @@
       <c r="G55" s="17">
         <v>-20250</v>
       </c>
-      <c r="H55" s="17">
-        <v>-20251</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
     </row>
-    <row r="57" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>2306</v>
       </c>
@@ -28641,14 +28322,11 @@
       <c r="G57" s="17">
         <v>-20253</v>
       </c>
-      <c r="H57" s="17">
-        <v>-20254</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
     </row>
-    <row r="59" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
         <v>2308</v>
       </c>
@@ -28670,14 +28348,11 @@
       <c r="G59" s="17">
         <v>-20259</v>
       </c>
-      <c r="H59" s="17">
-        <v>-20260</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
     </row>
-    <row r="61" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>2310</v>
       </c>
@@ -28691,7 +28366,7 @@
         <v>-20262</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>2312</v>
       </c>
@@ -28705,7 +28380,7 @@
         <v>-20264</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
         <v>2314</v>
       </c>
@@ -28719,7 +28394,7 @@
         <v>-20266</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>2316</v>
       </c>
@@ -31462,8 +31137,8 @@
       <c r="B79" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="C79" s="24" t="s">
-        <v>2657</v>
+      <c r="C79" s="24">
+        <v>27378</v>
       </c>
       <c r="D79" s="15">
         <v>27379</v>
@@ -47630,7 +47305,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74D234F7-04F3-48E7-AF82-BA19E5330384}">
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="9" customWidth="1"/>
@@ -47641,12 +47316,11 @@
     <col min="7" max="7" width="15.109375" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.44140625" style="9" customWidth="1"/>
     <col min="9" max="9" width="14.44140625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" style="9" customWidth="1"/>
-    <col min="11" max="256" width="9.109375" style="9" customWidth="1"/>
-    <col min="257" max="16384" width="11.44140625" style="9"/>
+    <col min="10" max="255" width="9.109375" style="9" customWidth="1"/>
+    <col min="256" max="16384" width="11.44140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>2631</v>
       </c>
@@ -47674,11 +47348,8 @@
       <c r="I1" s="23" t="s">
         <v>2639</v>
       </c>
-      <c r="J1" s="23" t="s">
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>0</v>
       </c>
@@ -47706,24 +47377,21 @@
       <c r="I2" s="23">
         <v>100</v>
       </c>
-      <c r="J2" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:9" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
     </row>
-    <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="13" t="s">
         <v>2</v>
       </c>
@@ -47745,11 +47413,8 @@
       <c r="I6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>1105</v>
       </c>
@@ -47777,11 +47442,8 @@
       <c r="I7" s="17">
         <v>-4403</v>
       </c>
-      <c r="J7" s="17">
-        <v>-4404</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>1104</v>
       </c>
@@ -47809,11 +47471,8 @@
       <c r="I8" s="17">
         <v>-4411</v>
       </c>
-      <c r="J8" s="17">
-        <v>-4412</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>1103</v>
       </c>
@@ -47841,11 +47500,8 @@
       <c r="I9" s="17">
         <v>-4419</v>
       </c>
-      <c r="J9" s="17">
-        <v>-4420</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>1102</v>
       </c>
@@ -47873,11 +47529,8 @@
       <c r="I10" s="17">
         <v>-4427</v>
       </c>
-      <c r="J10" s="17">
-        <v>-4428</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>1101</v>
       </c>
@@ -47905,11 +47558,8 @@
       <c r="I11" s="17">
         <v>-4443</v>
       </c>
-      <c r="J11" s="17">
-        <v>-4444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>1100</v>
       </c>
@@ -47937,11 +47587,8 @@
       <c r="I12" s="17">
         <v>-4451</v>
       </c>
-      <c r="J12" s="17">
-        <v>-4452</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>1099</v>
       </c>
@@ -47969,11 +47616,8 @@
       <c r="I13" s="17">
         <v>-4467</v>
       </c>
-      <c r="J13" s="17">
-        <v>-4468</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>1098</v>
       </c>
@@ -48001,11 +47645,8 @@
       <c r="I14" s="17">
         <v>-4499</v>
       </c>
-      <c r="J14" s="17">
-        <v>-4500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>1097</v>
       </c>
@@ -48033,11 +47674,8 @@
       <c r="I15" s="17">
         <v>-4507</v>
       </c>
-      <c r="J15" s="17">
-        <v>-4508</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>1096</v>
       </c>
@@ -48065,11 +47703,8 @@
       <c r="I16" s="17">
         <v>-4515</v>
       </c>
-      <c r="J16" s="17">
-        <v>-4516</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>1095</v>
       </c>
@@ -48097,11 +47732,8 @@
       <c r="I17" s="17">
         <v>-4571</v>
       </c>
-      <c r="J17" s="17">
-        <v>-4572</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>1094</v>
       </c>
@@ -48129,19 +47761,16 @@
       <c r="I18" s="17">
         <v>-4579</v>
       </c>
-      <c r="J18" s="17">
-        <v>-4580</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
     </row>
-    <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="13" t="s">
         <v>2</v>
       </c>
@@ -48163,11 +47792,8 @@
       <c r="I21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>1093</v>
       </c>
@@ -48195,11 +47821,8 @@
       <c r="I22" s="17">
         <v>-4595</v>
       </c>
-      <c r="J22" s="17">
-        <v>-4596</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>1092</v>
       </c>
@@ -48227,11 +47850,8 @@
       <c r="I23" s="17">
         <v>-4603</v>
       </c>
-      <c r="J23" s="17">
-        <v>-4604</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>1091</v>
       </c>
@@ -48259,11 +47879,8 @@
       <c r="I24" s="17">
         <v>-4611</v>
       </c>
-      <c r="J24" s="17">
-        <v>-4612</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>1090</v>
       </c>
@@ -48291,11 +47908,8 @@
       <c r="I25" s="17">
         <v>-4619</v>
       </c>
-      <c r="J25" s="17">
-        <v>-4620</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>1089</v>
       </c>
@@ -48323,11 +47937,8 @@
       <c r="I26" s="17">
         <v>-4635</v>
       </c>
-      <c r="J26" s="17">
-        <v>-4636</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>1088</v>
       </c>
@@ -48355,11 +47966,8 @@
       <c r="I27" s="17">
         <v>-4643</v>
       </c>
-      <c r="J27" s="17">
-        <v>-4644</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>1087</v>
       </c>
@@ -48387,11 +47995,8 @@
       <c r="I28" s="17">
         <v>-4659</v>
       </c>
-      <c r="J28" s="17">
-        <v>-4660</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>1086</v>
       </c>
@@ -48419,11 +48024,8 @@
       <c r="I29" s="17">
         <v>-4691</v>
       </c>
-      <c r="J29" s="17">
-        <v>-4692</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>1085</v>
       </c>
@@ -48451,11 +48053,8 @@
       <c r="I30" s="17">
         <v>-4699</v>
       </c>
-      <c r="J30" s="17">
-        <v>-4700</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>1084</v>
       </c>
@@ -48483,11 +48082,8 @@
       <c r="I31" s="17">
         <v>-4707</v>
       </c>
-      <c r="J31" s="17">
-        <v>-4708</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>1083</v>
       </c>
@@ -48515,11 +48111,8 @@
       <c r="I32" s="17">
         <v>-4763</v>
       </c>
-      <c r="J32" s="17">
-        <v>-4764</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>1082</v>
       </c>
@@ -48547,19 +48140,16 @@
       <c r="I33" s="17">
         <v>-4771</v>
       </c>
-      <c r="J33" s="17">
-        <v>-4772</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
     </row>
-    <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="13" t="s">
         <v>2</v>
       </c>
@@ -48581,11 +48171,8 @@
       <c r="I36" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>1081</v>
       </c>
@@ -48613,11 +48200,8 @@
       <c r="I37" s="17">
         <v>-4787</v>
       </c>
-      <c r="J37" s="17">
-        <v>-4788</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>1079</v>
       </c>
@@ -48645,11 +48229,8 @@
       <c r="I38" s="17">
         <v>-4795</v>
       </c>
-      <c r="J38" s="17">
-        <v>-4796</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>1077</v>
       </c>
@@ -48677,11 +48258,8 @@
       <c r="I39" s="17">
         <v>-4803</v>
       </c>
-      <c r="J39" s="17">
-        <v>-4804</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>1076</v>
       </c>
@@ -48709,11 +48287,8 @@
       <c r="I40" s="17">
         <v>-4811</v>
       </c>
-      <c r="J40" s="17">
-        <v>-4812</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>1074</v>
       </c>
@@ -48741,11 +48316,8 @@
       <c r="I41" s="17">
         <v>-4827</v>
       </c>
-      <c r="J41" s="17">
-        <v>-4828</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>1072</v>
       </c>
@@ -48773,11 +48345,8 @@
       <c r="I42" s="17">
         <v>-4835</v>
       </c>
-      <c r="J42" s="17">
-        <v>-4836</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>1070</v>
       </c>
@@ -48805,11 +48374,8 @@
       <c r="I43" s="17">
         <v>-4851</v>
       </c>
-      <c r="J43" s="17">
-        <v>-4852</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>1068</v>
       </c>
@@ -48837,11 +48403,8 @@
       <c r="I44" s="17">
         <v>-4883</v>
       </c>
-      <c r="J44" s="17">
-        <v>-4884</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>1066</v>
       </c>
@@ -48869,11 +48432,8 @@
       <c r="I45" s="17">
         <v>-4891</v>
       </c>
-      <c r="J45" s="17">
-        <v>-4892</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>1065</v>
       </c>
@@ -48901,11 +48461,8 @@
       <c r="I46" s="17">
         <v>-4899</v>
       </c>
-      <c r="J46" s="17">
-        <v>-4900</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>1064</v>
       </c>
@@ -48933,11 +48490,8 @@
       <c r="I47" s="17">
         <v>-4955</v>
       </c>
-      <c r="J47" s="17">
-        <v>-4956</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>1063</v>
       </c>
@@ -48965,11 +48519,8 @@
       <c r="I48" s="17">
         <v>-4963</v>
       </c>
-      <c r="J48" s="17">
-        <v>-4964</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="C49" s="17">
         <v>0</v>
@@ -48992,11 +48543,8 @@
       <c r="I49" s="17">
         <v>0</v>
       </c>
-      <c r="J49" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
         <v>1062</v>
       </c>
@@ -49024,14 +48572,11 @@
       <c r="I50" s="17">
         <v>-4971</v>
       </c>
-      <c r="J50" s="17">
-        <v>-4972</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
     </row>
-    <row r="52" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>1061</v>
       </c>
@@ -49059,11 +48604,8 @@
       <c r="I52" s="17">
         <v>-4979</v>
       </c>
-      <c r="J52" s="17">
-        <v>-4980</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>1060</v>
       </c>
@@ -49091,14 +48633,11 @@
       <c r="I53" s="17">
         <v>-4987</v>
       </c>
-      <c r="J53" s="17">
-        <v>-4988</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
     </row>
-    <row r="55" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
         <v>1059</v>
       </c>
@@ -49126,14 +48665,11 @@
       <c r="I55" s="17">
         <v>-5003</v>
       </c>
-      <c r="J55" s="17">
-        <v>-5004</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
     </row>
-    <row r="57" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H57" s="13" t="s">
         <v>7</v>
       </c>
@@ -49141,7 +48677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="12.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>1058</v>
       </c>
@@ -49155,10 +48691,10 @@
         <v>-5010</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
     </row>
-    <row r="60" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>1057</v>
       </c>
@@ -49172,10 +48708,10 @@
         <v>-5014</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
     </row>
-    <row r="62" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
         <v>1056</v>
       </c>
@@ -49189,10 +48725,10 @@
         <v>-5016</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
     </row>
-    <row r="64" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>1055</v>
       </c>
@@ -49219,9 +48755,6 @@
       </c>
       <c r="I64" s="17">
         <v>-5023</v>
-      </c>
-      <c r="J64" s="17">
-        <v>-5024</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/GRID_TO_LOAD.xlsx
+++ b/GRID_TO_LOAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhino\Documents\PROJEKTS JS\Mapping is boring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32251B46-FD46-4011-9F57-A0BE9A317EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62608D0F-8A56-4241-95D9-9C8E84A83463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="11" activeTab="18" xr2:uid="{B34349A9-D588-42E5-9EA3-3BAC4BC5A281}"/>
   </bookViews>
@@ -8036,9 +8036,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\+#"/>
-  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -8090,7 +8087,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8106,6 +8103,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8138,7 +8141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -8205,8 +8208,17 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -31067,31 +31079,31 @@
       <c r="A76" s="14" t="s">
         <v>2519</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="27" t="s">
         <v>2520</v>
       </c>
-      <c r="C76" s="15">
+      <c r="C76" s="26">
         <v>27342</v>
       </c>
-      <c r="D76" s="15">
+      <c r="D76" s="26">
         <v>27343</v>
       </c>
-      <c r="E76" s="15">
+      <c r="E76" s="26">
         <v>27344</v>
       </c>
-      <c r="F76" s="15">
+      <c r="F76" s="26">
         <v>27349</v>
       </c>
-      <c r="G76" s="15">
+      <c r="G76" s="26">
         <v>27350</v>
       </c>
-      <c r="H76" s="15">
+      <c r="H76" s="26">
         <v>27351</v>
       </c>
-      <c r="I76" s="15">
+      <c r="I76" s="26">
         <v>27352</v>
       </c>
-      <c r="J76" s="15">
+      <c r="J76" s="26">
         <v>527351</v>
       </c>
     </row>
@@ -31138,28 +31150,28 @@
         <v>203</v>
       </c>
       <c r="C79" s="24">
-        <v>27378</v>
-      </c>
-      <c r="D79" s="15">
-        <v>27379</v>
-      </c>
-      <c r="E79" s="15">
-        <v>27380</v>
-      </c>
-      <c r="F79" s="15">
-        <v>27385</v>
-      </c>
-      <c r="G79" s="15">
-        <v>27386</v>
-      </c>
-      <c r="H79" s="15">
-        <v>27387</v>
-      </c>
-      <c r="I79" s="15">
-        <v>27388</v>
-      </c>
-      <c r="J79" s="15">
-        <v>527387</v>
+        <v>27378.9</v>
+      </c>
+      <c r="D79" s="25">
+        <v>27379.9</v>
+      </c>
+      <c r="E79" s="25">
+        <v>27380.9</v>
+      </c>
+      <c r="F79" s="25">
+        <v>27385.9</v>
+      </c>
+      <c r="G79" s="25">
+        <v>27386.9</v>
+      </c>
+      <c r="H79" s="25">
+        <v>27387.9</v>
+      </c>
+      <c r="I79" s="25">
+        <v>27388.9</v>
+      </c>
+      <c r="J79" s="25">
+        <v>527387.9</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31242,29 +31254,29 @@
       <c r="B85" s="14" t="s">
         <v>2528</v>
       </c>
-      <c r="C85" s="15">
-        <v>27432</v>
-      </c>
-      <c r="D85" s="15">
-        <v>27433</v>
-      </c>
-      <c r="E85" s="15">
-        <v>27434</v>
-      </c>
-      <c r="F85" s="15">
-        <v>27439</v>
-      </c>
-      <c r="G85" s="15">
-        <v>27440</v>
-      </c>
-      <c r="H85" s="15">
-        <v>27441</v>
-      </c>
-      <c r="I85" s="15">
-        <v>27442</v>
-      </c>
-      <c r="J85" s="15">
-        <v>527441</v>
+      <c r="C85" s="25">
+        <v>27432.9</v>
+      </c>
+      <c r="D85" s="25">
+        <v>27433.9</v>
+      </c>
+      <c r="E85" s="25">
+        <v>27434.9</v>
+      </c>
+      <c r="F85" s="25">
+        <v>27439.9</v>
+      </c>
+      <c r="G85" s="25">
+        <v>27440.9</v>
+      </c>
+      <c r="H85" s="25">
+        <v>27441.9</v>
+      </c>
+      <c r="I85" s="25">
+        <v>27442.9</v>
+      </c>
+      <c r="J85" s="25">
+        <v>527441.9</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31312,29 +31324,29 @@
       <c r="B89" s="14" t="s">
         <v>2532</v>
       </c>
-      <c r="C89" s="15">
-        <v>27468</v>
-      </c>
-      <c r="D89" s="15">
-        <v>27469</v>
-      </c>
-      <c r="E89" s="15">
-        <v>27470</v>
-      </c>
-      <c r="F89" s="15">
-        <v>27475</v>
-      </c>
-      <c r="G89" s="15">
-        <v>27476</v>
-      </c>
-      <c r="H89" s="15">
-        <v>27477</v>
-      </c>
-      <c r="I89" s="15">
-        <v>27478</v>
-      </c>
-      <c r="J89" s="15">
-        <v>527477</v>
+      <c r="C89" s="25">
+        <v>27468.9</v>
+      </c>
+      <c r="D89" s="25">
+        <v>27469.9</v>
+      </c>
+      <c r="E89" s="25">
+        <v>27470.9</v>
+      </c>
+      <c r="F89" s="25">
+        <v>27475.9</v>
+      </c>
+      <c r="G89" s="25">
+        <v>27476.9</v>
+      </c>
+      <c r="H89" s="25">
+        <v>27477.9</v>
+      </c>
+      <c r="I89" s="25">
+        <v>27478.9</v>
+      </c>
+      <c r="J89" s="25">
+        <v>527477.9</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -31478,29 +31490,29 @@
       <c r="B96" s="14" t="s">
         <v>2542</v>
       </c>
-      <c r="C96" s="15">
-        <v>27558</v>
-      </c>
-      <c r="D96" s="15">
-        <v>27559</v>
-      </c>
-      <c r="E96" s="15">
-        <v>27560</v>
-      </c>
-      <c r="F96" s="15">
-        <v>27565</v>
-      </c>
-      <c r="G96" s="15">
-        <v>27566</v>
-      </c>
-      <c r="H96" s="15">
-        <v>27567</v>
-      </c>
-      <c r="I96" s="15">
-        <v>27568</v>
-      </c>
-      <c r="J96" s="15">
-        <v>527567</v>
+      <c r="C96" s="25">
+        <v>27558.9</v>
+      </c>
+      <c r="D96" s="25">
+        <v>27559.9</v>
+      </c>
+      <c r="E96" s="25">
+        <v>27560.9</v>
+      </c>
+      <c r="F96" s="25">
+        <v>27565.9</v>
+      </c>
+      <c r="G96" s="25">
+        <v>27566.9</v>
+      </c>
+      <c r="H96" s="25">
+        <v>27567.9</v>
+      </c>
+      <c r="I96" s="25">
+        <v>27568.9</v>
+      </c>
+      <c r="J96" s="25">
+        <v>527567.9</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
